--- a/Datas/__tables__.xlsx
+++ b/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="105">
   <si>
     <t>##var</t>
   </si>
@@ -278,18 +278,30 @@
     <t>亚克东技能数值表</t>
   </si>
   <si>
-    <t>HuntingConfig.TbLucky</t>
-  </si>
-  <si>
-    <t>Lucky</t>
-  </si>
-  <si>
-    <t>Lucky.xlsx</t>
+    <t>HuntingConfig.TbLuckyBuff</t>
+  </si>
+  <si>
+    <t>LuckyBuff</t>
+  </si>
+  <si>
+    <t>LuckyBuff.xlsx</t>
   </si>
   <si>
     <t>幸运仪式数值表</t>
   </si>
   <si>
+    <t>HuntingConfig.TbLuckyGift</t>
+  </si>
+  <si>
+    <t>LuckyGift</t>
+  </si>
+  <si>
+    <t>LuckyGift.xlsx</t>
+  </si>
+  <si>
+    <t>道具数值表</t>
+  </si>
+  <si>
     <t>HuntingConfig.Prop.TbProp</t>
   </si>
   <si>
@@ -299,7 +311,7 @@
     <t>Prop.xlsx</t>
   </si>
   <si>
-    <t>道具数值表</t>
+    <t>炮火轰炸道具数值表</t>
   </si>
   <si>
     <t>HuntingConfig.Prop.TbPropBombardment</t>
@@ -311,7 +323,7 @@
     <t>PropBombardment.xlsx</t>
   </si>
   <si>
-    <t>炮火轰炸道具数值表</t>
+    <t>指哪打哪道具数值表</t>
   </si>
   <si>
     <t>HuntingConfig.Prop.TbPropAimAssist</t>
@@ -321,9 +333,6 @@
   </si>
   <si>
     <t>PropAimAssist.xlsx</t>
-  </si>
-  <si>
-    <t>指哪打哪道具数值表</t>
   </si>
   <si>
     <t>HuntingConfig.Prop.TbPropTrap</t>
@@ -1289,7 +1298,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -1714,6 +1723,20 @@
         <v>101</v>
       </c>
     </row>
+    <row r="23" spans="2:9">
+      <c r="B23" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Datas/__tables__.xlsx
+++ b/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="101">
   <si>
     <t>##var</t>
   </si>
@@ -132,18 +132,6 @@
   </si>
   <si>
     <t>物种数值表</t>
-  </si>
-  <si>
-    <t>HuntingConfig.TbSpawn</t>
-  </si>
-  <si>
-    <t>Spawn</t>
-  </si>
-  <si>
-    <t>Spawn.xlsx</t>
-  </si>
-  <si>
-    <t>派发数值表</t>
   </si>
   <si>
     <t>HuntingConfig.TbMap</t>
@@ -1298,7 +1286,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -1692,7 +1680,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1" spans="2:9">
+    <row r="21" spans="2:9">
       <c r="B21" s="2" t="s">
         <v>95</v>
       </c>
@@ -1705,36 +1693,19 @@
       <c r="E21" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>98</v>
-      </c>
     </row>
     <row r="22" spans="2:9">
       <c r="B22" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="D22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9">
-      <c r="B23" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/__tables__.xlsx
+++ b/Datas/__tables__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="105">
   <si>
     <t>##var</t>
   </si>
@@ -108,6 +108,18 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>HuntingConfig.TbGlobal</t>
+  </si>
+  <si>
+    <t>Global</t>
+  </si>
+  <si>
+    <t>Global.xlsx</t>
+  </si>
+  <si>
+    <t>全局数值表</t>
   </si>
   <si>
     <t>HuntingConfig.TbBullet</t>
@@ -1286,7 +1298,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -1391,7 +1403,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:11">
+    <row r="4" customFormat="1" ht="28" customHeight="1" spans="1:11">
+      <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1404,11 +1417,15 @@
       <c r="E4" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:11">
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" ht="28" customHeight="1" spans="2:9">
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
@@ -1425,7 +1442,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:11">
+    <row r="6" ht="28" customHeight="1" spans="2:9">
       <c r="B6" s="2" t="s">
         <v>35</v>
       </c>
@@ -1442,7 +1459,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:11">
+    <row r="7" ht="28" customHeight="1" spans="2:9">
       <c r="B7" s="2" t="s">
         <v>39</v>
       </c>
@@ -1459,7 +1476,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1" spans="1:11">
+    <row r="8" ht="28" customHeight="1" spans="2:9">
       <c r="B8" s="2" t="s">
         <v>43</v>
       </c>
@@ -1476,7 +1493,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1" spans="1:11">
+    <row r="9" ht="28" customHeight="1" spans="2:9">
       <c r="B9" s="2" t="s">
         <v>47</v>
       </c>
@@ -1493,7 +1510,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1" spans="1:11">
+    <row r="10" ht="28" customHeight="1" spans="2:9">
       <c r="B10" s="2" t="s">
         <v>51</v>
       </c>
@@ -1510,7 +1527,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1" spans="1:11">
+    <row r="11" ht="28" customHeight="1" spans="2:9">
       <c r="B11" s="2" t="s">
         <v>55</v>
       </c>
@@ -1527,7 +1544,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1" spans="1:11">
+    <row r="12" ht="28" customHeight="1" spans="2:9">
       <c r="B12" s="2" t="s">
         <v>59</v>
       </c>
@@ -1544,7 +1561,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1" spans="1:11">
+    <row r="13" ht="28" customHeight="1" spans="2:9">
       <c r="B13" s="2" t="s">
         <v>63</v>
       </c>
@@ -1561,7 +1578,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1" spans="1:11">
+    <row r="14" ht="28" customHeight="1" spans="2:9">
       <c r="B14" s="2" t="s">
         <v>67</v>
       </c>
@@ -1578,7 +1595,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1" spans="1:11">
+    <row r="15" ht="28" customHeight="1" spans="2:9">
       <c r="B15" s="2" t="s">
         <v>71</v>
       </c>
@@ -1595,7 +1612,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1" spans="1:11">
+    <row r="16" ht="28" customHeight="1" spans="2:9">
       <c r="B16" s="2" t="s">
         <v>75</v>
       </c>
@@ -1680,7 +1697,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="2:9">
+    <row r="21" ht="28" customHeight="1" spans="2:9">
       <c r="B21" s="2" t="s">
         <v>95</v>
       </c>
@@ -1693,19 +1710,36 @@
       <c r="E21" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="22" spans="2:9">
+      <c r="I21" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
       <c r="B22" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D22" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
